--- a/stacked_model/results/candidates/bo_top_candidates.xlsx
+++ b/stacked_model/results/candidates/bo_top_candidates.xlsx
@@ -497,19 +497,19 @@
         <v>959.2222212006562</v>
       </c>
       <c r="F2" t="n">
-        <v>3.054853077716411</v>
+        <v>3.054853077716398</v>
       </c>
       <c r="G2" t="n">
         <v>4.911296439845443</v>
       </c>
       <c r="H2" t="n">
-        <v>90.6398084036133</v>
+        <v>90.63981244359209</v>
       </c>
       <c r="I2" t="n">
-        <v>6.124067204543739</v>
+        <v>5.958147515790889</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9119235665300374</v>
+        <v>0.9106270389875044</v>
       </c>
     </row>
     <row r="3">
@@ -529,19 +529,19 @@
         <v>934.4784837879893</v>
       </c>
       <c r="F3" t="n">
-        <v>2.796265769646185</v>
+        <v>2.796265769646167</v>
       </c>
       <c r="G3" t="n">
-        <v>5.842139841967368</v>
+        <v>5.842139841967365</v>
       </c>
       <c r="H3" t="n">
-        <v>89.75866628974364</v>
+        <v>89.75865251071539</v>
       </c>
       <c r="I3" t="n">
-        <v>7.659917675053562</v>
+        <v>7.527948010341123</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9064185059154505</v>
+        <v>0.9064759173649115</v>
       </c>
     </row>
     <row r="4">
@@ -561,19 +561,19 @@
         <v>929.8717425622768</v>
       </c>
       <c r="F4" t="n">
-        <v>2.829558566575855</v>
+        <v>2.829558566575798</v>
       </c>
       <c r="G4" t="n">
-        <v>5.897459292430044</v>
+        <v>5.897459292430039</v>
       </c>
       <c r="H4" t="n">
-        <v>89.76512460309408</v>
+        <v>89.76510962162777</v>
       </c>
       <c r="I4" t="n">
-        <v>7.645550143864765</v>
+        <v>7.513329003516862</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9058836419039309</v>
+        <v>0.9059289015589671</v>
       </c>
     </row>
     <row r="5">
@@ -581,31 +581,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.98133423630042</v>
+        <v>-0.9881842858468689</v>
       </c>
       <c r="C5" t="n">
-        <v>1.395349209768287</v>
+        <v>1.197944811492324</v>
       </c>
       <c r="D5" t="n">
-        <v>1.105470462499802</v>
+        <v>1.147634932324883</v>
       </c>
       <c r="E5" t="n">
-        <v>985.0107317824941</v>
+        <v>933.5863365500767</v>
       </c>
       <c r="F5" t="n">
-        <v>3.747264497291497</v>
+        <v>3.206224269650008</v>
       </c>
       <c r="G5" t="n">
-        <v>5.067471482717012</v>
+        <v>5.873811846390021</v>
       </c>
       <c r="H5" t="n">
-        <v>90.39985645846278</v>
+        <v>89.65560004584962</v>
       </c>
       <c r="I5" t="n">
-        <v>6.308978039494022</v>
+        <v>7.585275892952789</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9036187011138791</v>
+        <v>0.9027786609691375</v>
       </c>
     </row>
     <row r="6">
@@ -613,31 +613,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.9881842858468689</v>
+        <v>-0.98133423630042</v>
       </c>
       <c r="C6" t="n">
-        <v>1.197944811492324</v>
+        <v>1.395349209768287</v>
       </c>
       <c r="D6" t="n">
-        <v>1.147634932324883</v>
+        <v>1.105470462499802</v>
       </c>
       <c r="E6" t="n">
-        <v>933.5863365500767</v>
+        <v>985.0107317824941</v>
       </c>
       <c r="F6" t="n">
-        <v>3.20622426965001</v>
+        <v>3.747264497291508</v>
       </c>
       <c r="G6" t="n">
-        <v>5.873811846390026</v>
+        <v>5.067471482717011</v>
       </c>
       <c r="H6" t="n">
-        <v>89.65561914260337</v>
+        <v>90.39985262243552</v>
       </c>
       <c r="I6" t="n">
-        <v>7.716262405861235</v>
+        <v>6.148057097071797</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9027215843767187</v>
+        <v>0.9024103768579635</v>
       </c>
     </row>
     <row r="7">
@@ -645,31 +645,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.9779437557508321</v>
+        <v>-0.9753529106293825</v>
       </c>
       <c r="C7" t="n">
-        <v>1.137208374331435</v>
+        <v>1.501908700020724</v>
       </c>
       <c r="D7" t="n">
-        <v>1.034730357262841</v>
+        <v>1.121024007782774</v>
       </c>
       <c r="E7" t="n">
-        <v>931.7453413415755</v>
+        <v>992.2539094228936</v>
       </c>
       <c r="F7" t="n">
-        <v>2.840062785113513</v>
+        <v>3.796557778379044</v>
       </c>
       <c r="G7" t="n">
-        <v>3.747907256253344</v>
+        <v>5.42621810723347</v>
       </c>
       <c r="H7" t="n">
-        <v>91.1673747434628</v>
+        <v>90.06757441015667</v>
       </c>
       <c r="I7" t="n">
-        <v>4.50137399483912</v>
+        <v>6.647340254345798</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9000604278246109</v>
+        <v>0.8978589362522136</v>
       </c>
     </row>
     <row r="8">
@@ -677,31 +677,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.9753529106293825</v>
+        <v>-0.9779437557508321</v>
       </c>
       <c r="C8" t="n">
-        <v>1.501908700020724</v>
+        <v>1.137208374331435</v>
       </c>
       <c r="D8" t="n">
-        <v>1.121024007782774</v>
+        <v>1.034730357262841</v>
       </c>
       <c r="E8" t="n">
-        <v>992.2539094228936</v>
+        <v>931.7453413415755</v>
       </c>
       <c r="F8" t="n">
-        <v>3.796557778379082</v>
+        <v>2.840062785113556</v>
       </c>
       <c r="G8" t="n">
-        <v>5.426218107233474</v>
+        <v>3.747907256253351</v>
       </c>
       <c r="H8" t="n">
-        <v>90.0675843031344</v>
+        <v>91.16739659197755</v>
       </c>
       <c r="I8" t="n">
-        <v>6.796441376870342</v>
+        <v>4.272865793738961</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8986386222758002</v>
+        <v>0.8963498694520261</v>
       </c>
     </row>
     <row r="9">
@@ -721,19 +721,19 @@
         <v>924.5040419813747</v>
       </c>
       <c r="F9" t="n">
-        <v>3.163171815034923</v>
+        <v>3.163171815034922</v>
       </c>
       <c r="G9" t="n">
-        <v>4.205589412116763</v>
+        <v>4.20558941211676</v>
       </c>
       <c r="H9" t="n">
-        <v>90.89747562682783</v>
+        <v>90.8974872927856</v>
       </c>
       <c r="I9" t="n">
-        <v>5.053048234033386</v>
+        <v>4.850611954098968</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8982522115234839</v>
+        <v>0.8954022848193597</v>
       </c>
     </row>
     <row r="10">
@@ -741,31 +741,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.9785128573232006</v>
+        <v>-0.9769674601801612</v>
       </c>
       <c r="C10" t="n">
-        <v>1.406855554262252</v>
+        <v>1.316069276597882</v>
       </c>
       <c r="D10" t="n">
-        <v>1.093271521061723</v>
+        <v>1.135957426920155</v>
       </c>
       <c r="E10" t="n">
-        <v>954.6524202513552</v>
+        <v>876.4872436174745</v>
       </c>
       <c r="F10" t="n">
-        <v>3.595719681393603</v>
+        <v>3.156527371826327</v>
       </c>
       <c r="G10" t="n">
-        <v>4.81113365811927</v>
+        <v>5.702982121395989</v>
       </c>
       <c r="H10" t="n">
-        <v>90.47749704831578</v>
+        <v>89.74993664942699</v>
       </c>
       <c r="I10" t="n">
-        <v>5.868595983977621</v>
+        <v>7.141809198787176</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8960284932598735</v>
+        <v>0.8949370991378428</v>
       </c>
     </row>
     <row r="11">
@@ -773,31 +773,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.9655488370277454</v>
+        <v>-0.9785128573232006</v>
       </c>
       <c r="C11" t="n">
-        <v>1.28033590853571</v>
+        <v>1.406855554262252</v>
       </c>
       <c r="D11" t="n">
-        <v>1.090765246824213</v>
+        <v>1.093271521061723</v>
       </c>
       <c r="E11" t="n">
-        <v>900.4017789127275</v>
+        <v>954.6524202513552</v>
       </c>
       <c r="F11" t="n">
-        <v>2.741086736601474</v>
+        <v>3.595719681393589</v>
       </c>
       <c r="G11" t="n">
-        <v>4.949545365567583</v>
+        <v>4.811133658119271</v>
       </c>
       <c r="H11" t="n">
-        <v>90.43862829771777</v>
+        <v>90.47749747073416</v>
       </c>
       <c r="I11" t="n">
-        <v>5.94793739178114</v>
+        <v>5.695238092836544</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8953718117164822</v>
+        <v>0.8942295736598881</v>
       </c>
     </row>
   </sheetData>
